--- a/assumptions_26_slides.xlsx
+++ b/assumptions_26_slides.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>858499.72</v>
+        <v>80518234.16</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>602423652.38</v>
+        <v>519134744.05</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12318638.98</v>
+        <v>63477731.09999999</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8889910.27</v>
+        <v>28616498.71000001</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4334200.73</v>
+        <v>10493226.73</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>549125651.48</v>
+        <v>484398996.92</v>
       </c>
       <c r="C8" t="n">
         <v>54400000</v>
       </c>
       <c r="D8" t="n">
-        <v>603525651.48</v>
+        <v>538798996.92</v>
       </c>
     </row>
     <row r="9">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6695432.629999999</v>
+        <v>19696040.26</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>555821084.11</v>
+        <v>504095037.1799999</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
